--- a/Template V2.0.xlsx
+++ b/Template V2.0.xlsx
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="642">
   <si>
     <t>Sr#</t>
   </si>
@@ -1575,7 +1575,7 @@
     </r>
   </si>
   <si>
-    <t>ROI in Rupees (Per Day)</t>
+    <t>ROI (Per Day)</t>
   </si>
   <si>
     <t>ROI In Percent</t>
@@ -1948,6 +1948,9 @@
   </si>
   <si>
     <t>Total Cost</t>
+  </si>
+  <si>
+    <t>ROI in Rupees (Per Day)</t>
   </si>
   <si>
     <t>Document Automation</t>
@@ -20379,7 +20382,7 @@
         <v>567</v>
       </c>
       <c r="AB2" s="59" t="s">
-        <v>455</v>
+        <v>568</v>
       </c>
       <c r="AC2" s="59" t="s">
         <v>456</v>
@@ -20414,7 +20417,7 @@
         <v>458</v>
       </c>
       <c r="X3" s="53" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Y3" s="51" t="s">
         <v>459</v>
@@ -23182,10 +23185,10 @@
       <c r="M1" s="30"/>
       <c r="N1" s="31"/>
       <c r="O1" s="32" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P1" s="32" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Q1" s="32" t="s">
         <v>563</v>
@@ -23235,19 +23238,19 @@
         <v>565</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J2" s="34" t="s">
         <v>555</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L2" s="35" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N2" s="36" t="s">
         <v>567</v>
@@ -23257,7 +23260,7 @@
       <c r="Q2" s="37"/>
       <c r="R2" s="37"/>
       <c r="S2" s="50" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="T2" s="51" t="s">
         <v>555</v>
@@ -23266,7 +23269,7 @@
         <v>558</v>
       </c>
       <c r="V2" s="49" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="W2" s="49"/>
       <c r="X2" s="49"/>
@@ -23278,7 +23281,7 @@
         <v>567</v>
       </c>
       <c r="AB2" s="59" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AC2" s="59" t="s">
         <v>456</v>
@@ -23313,7 +23316,7 @@
         <v>458</v>
       </c>
       <c r="X3" s="53" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Y3" s="51" t="s">
         <v>459</v>
@@ -28683,12 +28686,12 @@
         <v>387</v>
       </c>
       <c r="B1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B2">
         <v>200</v>
@@ -28696,7 +28699,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B3">
         <f>B2/12</f>
@@ -28713,7 +28716,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B5">
         <v>6.5</v>
@@ -28721,7 +28724,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B6">
         <v>60</v>
@@ -28729,7 +28732,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B7" s="15">
         <v>0.8</v>
@@ -28737,7 +28740,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B8" s="15">
         <v>0.7</v>
@@ -28745,7 +28748,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B9" s="15">
         <v>0.6</v>
@@ -28775,31 +28778,31 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="13" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B1" s="13"/>
       <c r="G1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B2" s="12">
         <v>6089</v>
@@ -28832,7 +28835,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B3" s="12">
         <v>200</v>
@@ -28865,7 +28868,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B4" s="12">
         <f>(B2/B3)*(B3/12)</f>
@@ -28900,7 +28903,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B5" s="12">
         <f>2.23/100</f>
@@ -28931,7 +28934,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B6" s="12">
         <v>49000</v>
@@ -28961,7 +28964,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B7" s="12">
         <f>B6/(B3/12)</f>
@@ -28992,7 +28995,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B8" s="12">
         <f>24*60</f>
@@ -29023,7 +29026,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B9" s="12">
         <f>B7/B8</f>
@@ -29054,7 +29057,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B10" s="12">
         <f>B4*B5</f>
@@ -29085,7 +29088,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B11" s="12">
         <f>B10*B9</f>
@@ -29428,7 +29431,7 @@
     </row>
     <row r="26" spans="8:9">
       <c r="H26" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I26">
         <f>SUM(I2:I24)/60</f>
@@ -29437,7 +29440,7 @@
     </row>
     <row r="27" spans="8:9">
       <c r="H27" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I27">
         <f>I26/(200/12)</f>
@@ -29446,7 +29449,7 @@
     </row>
     <row r="28" spans="8:15">
       <c r="H28" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I28">
         <f>I27/6.5</f>
@@ -29486,15 +29489,15 @@
     <row r="1" ht="53.45" customHeight="1"/>
     <row r="2" spans="1:2">
       <c r="A2" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B3" s="10">
         <v>200</v>
@@ -29502,7 +29505,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B4" s="10">
         <v>22</v>
@@ -29510,7 +29513,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B5" s="10">
         <v>6.5</v>
@@ -29518,7 +29521,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B6" s="11">
         <v>0.7</v>
@@ -29526,7 +29529,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B7" s="11">
         <v>0.8</v>
@@ -29534,7 +29537,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B8" s="11">
         <v>0.9</v>
@@ -29542,7 +29545,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B9" s="10">
         <v>5000</v>
@@ -29550,7 +29553,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B10" s="10">
         <v>60</v>
@@ -29558,7 +29561,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B11" s="10">
         <v>48000</v>
@@ -29566,7 +29569,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B12" s="10">
         <v>30</v>
@@ -29574,7 +29577,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B13" s="10">
         <v>10785</v>
@@ -29582,7 +29585,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B14" s="10">
         <v>5283</v>
@@ -29590,7 +29593,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="9" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B15" s="10">
         <v>6432</v>
@@ -29598,7 +29601,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B16" s="10">
         <v>5</v>
@@ -29606,7 +29609,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="9" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B17" s="10">
         <v>23</v>
@@ -29614,7 +29617,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="9" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B18" s="10">
         <v>365</v>
@@ -29622,7 +29625,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="9" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B19" s="10">
         <v>30</v>
@@ -29630,7 +29633,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="9" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B20" s="10">
         <v>24</v>
@@ -29638,7 +29641,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="9" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B21" s="10">
         <v>49000</v>
@@ -29646,7 +29649,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B22" s="10">
         <v>1400000</v>
@@ -29654,7 +29657,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B23" s="10">
         <v>21000</v>
@@ -29662,7 +29665,7 @@
     </row>
     <row r="24" ht="26" spans="1:2">
       <c r="A24" s="9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B24" s="10">
         <v>3</v>
@@ -29670,7 +29673,7 @@
     </row>
     <row r="25" ht="26" spans="1:2">
       <c r="A25" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B25" s="10">
         <v>50000</v>
@@ -29678,7 +29681,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B26" s="10">
         <v>150000</v>
@@ -29686,7 +29689,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B27" s="10">
         <v>100000</v>
@@ -29722,40 +29725,40 @@
   <sheetData>
     <row r="1" ht="24" spans="1:12">
       <c r="A1" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>312</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>459</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -30009,7 +30012,7 @@
     </row>
     <row r="9" ht="72" spans="3:3">
       <c r="C9" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
